--- a/tasks/finalpool/budget-variance-analysis-quarterly/groundtruth_workspace/budget_forecast.xlsx
+++ b/tasks/finalpool/budget-variance-analysis-quarterly/groundtruth_workspace/budget_forecast.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,35 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,12 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,56 +415,49 @@
   </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FY2024 Budget Forecast - Year-End Projection</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Scenario Analysis</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -503,41 +470,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3145000</v>
+        <v>3100000</v>
       </c>
       <c r="C5" t="n">
-        <v>3140000</v>
+        <v>3100000</v>
       </c>
       <c r="D5" t="n">
         <v>1860000</v>
       </c>
       <c r="E5" t="n">
-        <v>1220000</v>
+        <v>1200000</v>
       </c>
       <c r="F5" t="n">
-        <v>9365000</v>
+        <v>9260000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Conservative (Controls)</t>
+          <t>Conservative (Cost Controls)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3120000</v>
+        <v>3040000</v>
       </c>
       <c r="C6" t="n">
-        <v>3100000</v>
+        <v>3040000</v>
       </c>
       <c r="D6" t="n">
-        <v>1800000</v>
+        <v>1820000</v>
       </c>
       <c r="E6" t="n">
-        <v>1200000</v>
+        <v>1180000</v>
       </c>
       <c r="F6" t="n">
-        <v>9220000</v>
+        <v>9080000</v>
       </c>
     </row>
     <row r="7">
@@ -547,50 +514,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3140000</v>
+        <v>3180000</v>
       </c>
       <c r="C7" t="n">
-        <v>3280000</v>
+        <v>3190000</v>
       </c>
       <c r="D7" t="n">
-        <v>1900000</v>
+        <v>1910000</v>
       </c>
       <c r="E7" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" t="n">
-        <v>9560000</v>
-      </c>
-    </row>
+        <v>9520000</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Variance to Budget by Scenario</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Annual Budget</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Variance $</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Variance %</t>
         </is>
@@ -603,16 +572,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10800000</v>
+        <v>9180000</v>
       </c>
       <c r="C12" t="n">
-        <v>9365000</v>
+        <v>9260000</v>
       </c>
       <c r="D12" t="n">
-        <v>-1435000</v>
+        <v>80000</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -622,16 +591,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10800000</v>
+        <v>9180000</v>
       </c>
       <c r="C13" t="n">
-        <v>9220000</v>
+        <v>9080000</v>
       </c>
       <c r="D13" t="n">
-        <v>-1580000</v>
+        <v>-100000</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.6</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="14">
@@ -641,20 +610,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10800000</v>
+        <v>9180000</v>
       </c>
       <c r="C14" t="n">
-        <v>9560000</v>
+        <v>9520000</v>
       </c>
       <c r="D14" t="n">
-        <v>-1240000</v>
+        <v>340000</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.5</v>
-      </c>
-    </row>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Key Assumptions</t>
         </is>
@@ -663,42 +634,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>• Q4 spending follows Q3 patterns</t>
+          <t>Q2-Q4 spending follows Q1 patterns</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• No major one-time expenditures anticipated</t>
+          <t>No major one-time expenditures anticipated</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>• Control initiatives implemented in Q4</t>
+          <t>Control initiatives implemented in Q2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>• Sales revenue continues current trajectory</t>
+          <t>Sales revenue continues current trajectory</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>• IT emergency replacements completed in Q3</t>
+          <t>IT emergency replacements completed in Q1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>